--- a/Wochenplan/Wochenuebersicht_20260521.xlsx
+++ b/Wochenplan/Wochenuebersicht_20260521.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produktionsbedarf" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wochenplan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Produktionsbedarf" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Wochenplan" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Wochenplan/Wochenuebersicht_20260521.xlsx
+++ b/Wochenplan/Wochenuebersicht_20260521.xlsx
@@ -590,10 +590,10 @@
         <v>9</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>6</v>
@@ -618,10 +618,10 @@
         <v>9</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>12</v>
@@ -646,13 +646,13 @@
         <v>11</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0</v>
@@ -674,13 +674,13 @@
         <v>9</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>0</v>
@@ -702,13 +702,13 @@
         <v>8</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0</v>
@@ -811,7 +811,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>Lager OK (50&gt;=30)</t>
+          <t>Lager OK (40&gt;=30)</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>10x/0g</t>
+          <t>4x/0g</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -945,7 +945,7 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>Charge 1/5</t>
+          <t>Charge 1/2</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Charge 2/5</t>
+          <t>Charge 2/2</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       <c r="A6" s="14" t="inlineStr"/>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>Bienenstich</t>
+          <t>Donauwelle</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
@@ -977,7 +977,7 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>Charge 1/2</t>
+          <t>Charge 1/1</t>
         </is>
       </c>
     </row>
@@ -985,11 +985,11 @@
       <c r="A7" s="14" t="inlineStr"/>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Lauch-Speck Quiche</t>
+          <t>Kaese-Rhabarber Schnitte</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
@@ -998,18 +998,9 @@
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="14" t="inlineStr"/>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>Donauwelle</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>Charge 1/1</t>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>FREITAG</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1008,7 @@
       <c r="A9" s="14" t="inlineStr"/>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Kaese-Rhabarber Schnitte</t>
+          <t>Bienenstich</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
@@ -1025,92 +1016,21 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>Charge 1/2</t>
+          <t>Charge 1/1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>FREITAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="14" t="inlineStr"/>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>Kaesekuchen</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>Charge 3/5</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="14" t="inlineStr"/>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>Kaesekuchen</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>Charge 4/5</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="14" t="inlineStr"/>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>Bienenstich</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n">
+      <c r="A10" s="14" t="inlineStr"/>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Kaese-Rhabarber Schnitte</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>Charge 2/2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="14" t="inlineStr"/>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>Lauch-Speck Quiche</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>Charge 2/2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="14" t="inlineStr"/>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>Kaese-Rhabarber Schnitte</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Charge 2/2</t>
         </is>
@@ -1119,8 +1039,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A8:D8"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
